--- a/results/Int All Data 0.1/Linea_fi_all.xlsx
+++ b/results/Int All Data 0.1/Linea_fi_all.xlsx
@@ -1901,7 +1901,7 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>0.0018638265500189987 +/- 0.0008748573602129994</t>
+          <t>0.0019018638265499987 +/- 0.0009001262507568738</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0008758568164508706 +/- 0.00029742001812290434</t>
+          <t>0.0008377760853008343 +/- 0.00022848438690026282</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>-0.0029702970297029617 +/- 0.00241925059775605</t>
+          <t>-0.0029322162985529255 +/- 0.002474075532487532</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>0.0021325209444021387 +/- 0.0006854531607006775</t>
+          <t>0.002094440213252102 +/- 0.0006650513783919573</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.007281001137656451 +/- 0.003458176144157162</t>
+          <t>0.007243079256731155 +/- 0.0034980751237258705</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>-0.005233219567690528 +/- 0.001266840583124023</t>
+          <t>-0.005271141448615813 +/- 0.001329431030941075</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="EN4" t="inlineStr">
         <is>
-          <t>0.0021236253318164923 +/- 0.0009319837487633318</t>
+          <t>0.0021615472127417767 +/- 0.001004035062182292</t>
         </is>
       </c>
       <c r="EO4" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.0011836734693877692 +/- 0.0010557156862349157</t>
+          <t>0.001224489795918382 +/- 0.001125228469558399</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-0.021877551020408104 +/- 0.002409200745040612</t>
+          <t>-0.021918367346938715 +/- 0.002435678162911957</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0.0008421052631579328 +/- 0.0005480876965548612</t>
+          <t>0.0009122807017544199 +/- 0.0005011528721784558</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0.0006315789473684719 +/- 0.000465491198646374</t>
+          <t>0.0005964912280702284 +/- 0.0004452132470333195</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0004912280701754868 +/- 0.0004759529812719626</t>
+          <t>0.00045614035087724323 +/- 0.00044521324703333256</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.018112633181126336 +/- 0.0055435536838582475</t>
+          <t>0.018074581430745827 +/- 0.005485922317207581</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-0.009436834094368329 +/- 0.0019536526108056926</t>
+          <t>-0.00939878234398781 +/- 0.0019555045901871477</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-0.003006088280060859 +/- 0.004490912653692845</t>
+          <t>-0.003044140030441378 +/- 0.0044991267135030336</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.00803212851405627 +/- 0.0018034449120450428</t>
+          <t>0.008068638189120158 +/- 0.001857693206748227</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0286983391270761 +/- 0.0023875719521862645</t>
+          <t>0.028775589030513714 +/- 0.0023637081932474805</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.00030899961375048247 +/- 0.0005407493240633483</t>
+          <t>0.0002317497103128674 +/- 0.0006275811822816439</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="DX9" t="inlineStr">
         <is>
-          <t>0.0017381228273464888 +/- 0.0007578762792718648</t>
+          <t>0.0016994978756276757 +/- 0.000736917111948198</t>
         </is>
       </c>
       <c r="DY9" t="inlineStr">
@@ -7781,14 +7781,14 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
+          <t>0.008067473414008087 +/- 0.0011711565399832096</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
           <t>0.008030803080308058 +/- 0.0011296605647780882</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>0.008030803080308058 +/- 0.0011296605647780882</t>
-        </is>
-      </c>
       <c r="CA10" t="inlineStr">
         <is>
           <t>0.009570957095709608 +/- 0.0017848322000202281</t>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.01092775944261094 +/- 0.0009534286762009462</t>
+          <t>0.01096442977631098 +/- 0.0009196872903545522</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -8216,309 +8216,309 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>-0.005704441041347619 +/- 0.003357080518979773</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-0.0011485451761102383 +/- 0.0024988007461073246</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-7.656967840734552e-05 +/- 0.00015313935681469105</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-0.0005359877488514298 +/- 0.00030627871362940426</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>-0.0003445635528330548 +/- 0.00011485451761101826</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.00011485451761101828 +/- 0.0003445635528330548</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-0.0003445635528330548 +/- 0.00011485451761101826</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>-0.0005742725880551247 +/- 0.001225712909156346</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3.828483920368386e-05 +/- 0.0007929676560952245</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0.00011485451761102938 +/- 0.0006417708504685957</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0.0011485451761102604 +/- 0.0017544317362005516</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>-0.001607963246554356 +/- 0.0012558361000655997</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>-0.005666156202143946 +/- 0.0033542413650550604</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-0.0011485451761102383 +/- 0.0024988007461073246</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>-7.656967840734552e-05 +/- 0.00015313935681469105</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-0.0005359877488514298 +/- 0.00030627871362940426</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>-0.0003445635528330548 +/- 0.00011485451761101826</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.00011485451761101828 +/- 0.0003445635528330548</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-0.0003445635528330548 +/- 0.00011485451761101826</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>-0.0005742725880551247 +/- 0.001225712909156346</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3.828483920368386e-05 +/- 0.0007929676560952245</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.00011485451761102938 +/- 0.0006417708504685957</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-0.0056661562021439685 +/- 0.0019952242298308352</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.11198315467075037 +/- 0.006443350949351756</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.004173047473200619 +/- 0.0008637453424715415</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.00015313935681469105 +/- 0.0003508863472400865</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-0.001952526799387433 +/- 0.0015356945727512763</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3.828483920367276e-05 +/- 0.0002679938744257093</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.002297090352220521 +/- 0.0016599910711086556</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>-0.0002679938744257204 +/- 0.0005427812740718814</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>-0.0003828483920367609 +/- 0.0006173244830243909</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>-0.0018759571209800874 +/- 0.0009753245943994682</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.0011485451761102604 +/- 0.0017544317362005516</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>-0.001607963246554356 +/- 0.0012558361000655997</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-0.005666156202143946 +/- 0.0033542413650550604</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-0.0056661562021439685 +/- 0.0019952242298308352</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.11198315467075037 +/- 0.006443350949351756</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.004173047473200619 +/- 0.0008637453424715415</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.00015313935681469105 +/- 0.0003508863472400865</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.001952526799387433 +/- 0.0015356945727512763</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>3.828483920367276e-05 +/- 0.0002679938744257093</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>0.002297090352220521 +/- 0.0016599910711086556</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>-0.0002679938744257204 +/- 0.0005427812740718814</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>-0.0001914241960183638 +/- 0.0001914241960183638</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-0.00042113323124042256 +/- 0.0007929676560952617</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0.017036753445635523 +/- 0.003935152597330087</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.03522205206738129 +/- 0.0030723434376323014</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>-0.002182235834609503 +/- 0.0022974093703947095</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>0.07928790199081164 +/- 0.004646366446739481</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>-0.0002679938744257093 +/- 0.0003445635528330548</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>0.057082695252679935 +/- 0.0033744996553476832</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.001607963246554367 +/- 0.0008175404480881835</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-7.656967840734552e-05 +/- 0.0003337594903170275</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
         <is>
           <t>-0.0003828483920367609 +/- 0.0006173244830243909</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.0018759571209800874 +/- 0.0009753245943994682</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.007274119448698324 +/- 0.0017710617926830717</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.40356049004594186 +/- 0.009692115367437887</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>-0.0027182235834609437 +/- 0.0009902386796613745</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>-0.0026799387442572598 +/- 0.0010414602227209367</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>-0.007350689127105681 +/- 0.0015004531349360913</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>-0.001225114854517606 +/- 0.0004464741113970504</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0.09808575803981623 +/- 0.0038922710649736177</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>0.003981623277182211 +/- 0.0011253398512020766</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>0.009954058192955573 +/- 0.0016862722469789613</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>0.018415007656967842 +/- 0.004336339034596941</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>0.00015313935681470213 +/- 0.0007883330888964052</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>-0.0009188361408882017 +/- 0.00045941807044411935</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.008652373660030622 +/- 0.0013284342705128258</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>-0.006125574272588053 +/- 0.0013697200474730633</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0.00011485451761102938 +/- 0.0005943405320160669</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>0.012480857580398163 +/- 0.003373413594473321</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>0.20513016845329252 +/- 0.007419360824966165</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>0.00647013782542113 +/- 0.003016738440749126</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>0.04552067381316997 +/- 0.0043058106110993605</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.003330781010719741 +/- 0.0006859292828165817</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.018721286370597234 +/- 0.0035065652496295277</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>0.009954058192955573 +/- 0.0016862722469789613</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>0.004249617151607943 +/- 0.0034856028113691216</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-0.0008422664624808563 +/- 0.0015198647198529348</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-0.0001914241960183638 +/- 0.0001914241960183638</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-0.00042113323124042256 +/- 0.0007929676560952617</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0.017036753445635523 +/- 0.003935152597330087</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>0.03522205206738129 +/- 0.0030723434376323014</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>-0.002182235834609503 +/- 0.0022974093703947095</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>0.07928790199081164 +/- 0.004646366446739481</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>-0.0002679938744257093 +/- 0.0003445635528330548</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>0.057082695252679935 +/- 0.0033744996553476832</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>0.001607963246554367 +/- 0.0008175404480881835</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-7.656967840734552e-05 +/- 0.0003337594903170275</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.0003828483920367609 +/- 0.0006173244830243909</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>0.007274119448698324 +/- 0.0017710617926830717</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>0.40356049004594186 +/- 0.009692115367437887</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>-0.0027182235834609437 +/- 0.0009902386796613745</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>-0.0026799387442572598 +/- 0.0010414602227209367</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>-0.007350689127105681 +/- 0.0015004531349360913</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>-0.001225114854517606 +/- 0.0004464741113970504</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>0.09808575803981623 +/- 0.0038922710649736177</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>0.003981623277182211 +/- 0.0011253398512020766</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>0.009954058192955573 +/- 0.0016862722469789613</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>0.018415007656967842 +/- 0.004336339034596941</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>0.00015313935681470213 +/- 0.0007883330888964052</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>-0.0009188361408882017 +/- 0.00045941807044411935</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.008652373660030622 +/- 0.0013284342705128258</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>-0.006125574272588053 +/- 0.0013697200474730633</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.00011485451761102938 +/- 0.0005943405320160669</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>0.012480857580398163 +/- 0.003373413594473321</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>0.20513016845329252 +/- 0.007419360824966165</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>0.00647013782542113 +/- 0.003016738440749126</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>0.04552067381316997 +/- 0.0043058106110993605</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.003330781010719741 +/- 0.0006859292828165817</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.018721286370597234 +/- 0.0035065652496295277</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>0.009954058192955573 +/- 0.0016862722469789613</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>0.004249617151607943 +/- 0.0034856028113691216</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-0.0008422664624808563 +/- 0.0015198647198529348</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="BR11" t="inlineStr">
         <is>
           <t>-0.002871362940275657 +/- 0.0015992801358503449</t>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>0.00011485451761101828 +/- 0.00029901415298262354</t>
+          <t>7.656967840734552e-05 +/- 0.0002864975028157495</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>0.024349157733537508 +/- 0.0037869105723976238</t>
+          <t>0.02438744257274118 +/- 0.0038133314233616657</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
